--- a/lib/plantillas-aseguradoras/axa-colpatria.xlsx
+++ b/lib/plantillas-aseguradoras/axa-colpatria.xlsx
@@ -411,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,7 +452,7 @@
   <autoFilter ref="A1:L33"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/lib/plantillas-aseguradoras/axa-colpatria.xlsx
+++ b/lib/plantillas-aseguradoras/axa-colpatria.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Relacion_cert" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relacion_cert'!A1:L33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relacion_cert'!A1:L31</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -432,6 +432,9 @@
       <c r="F1" t="str">
         <v>BENEFICIARIO</v>
       </c>
+      <c r="G1" t="str">
+        <v>NIT</v>
+      </c>
       <c r="H1" t="str">
         <v>PROPIETARIO</v>
       </c>
@@ -449,7 +452,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L33"/>
+  <autoFilter ref="A1:L31"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
